--- a/submission/egfr_analysis.xlsx
+++ b/submission/egfr_analysis.xlsx
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Soumission'!$A$1:$Y$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Classement complet'!$A$1:$AZ$36</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Paires WT-mutant'!$A$1:$S$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Paires WT-mutant'!$A$1:$U$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PROPKA pKa des DE'!$A$1:$J$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PROPKA scan non biaise'!$A$1:$H$181</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Geometrie ponts WT'!$A$1:$O$24</definedName>
@@ -1133,7 +1133,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1256,7 +1256,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1379,7 +1379,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1502,7 +1502,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1625,7 +1625,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1748,7 +1748,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1871,7 +1871,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1994,7 +1994,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2117,7 +2117,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2504,17 +2504,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cd272a8fd929c7ee</t>
+          <t>a6d2f6834f22e574</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>N21E</t>
+          <t>S44D</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2534,29 +2534,29 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ROUGE</t>
+          <t>VERT</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste' ; verdict_carboxylate='ROUGE' attendu 'VERT'</t>
+          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste'</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0</t>
+          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cd272a8fd929c7ee</t>
+          <t>f6d5f550a210fd48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -2566,39 +2566,39 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>N21E</t>
+          <t>S38D</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ROUGE</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste' ; verdict_carboxylate='ROUGE' attendu 'VERT'</t>
+          <t>mutant non eligible : mecanisme_pH='INDETERMINE' attendu 'robuste' ; verdict_carboxylate='INDETERMINE' attendu 'VERT'</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>a6d2f6834f22e574</t>
+          <t>5b295c4d9e1ff73f</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -2608,7 +2608,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>S44D</t>
+          <t>H23E</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2618,29 +2618,29 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>VERT</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste'</t>
+          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste' ; verdict_carboxylate='INDETERMINE' attendu 'VERT'</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1e7ab6d8f00c9958</t>
+          <t>5b295c4d9e1ff73f</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -2650,22 +2650,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>S28D</t>
+          <t>H23E</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>INDETERMINE</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>INDETERMINE</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>mutant non eligible : mecanisme_pH='INDETERMINE' attendu 'robuste' ; verdict_carboxylate='INDETERMINE' attendu 'VERT'</t>
+          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste' ; verdict_carboxylate='INDETERMINE' attendu 'VERT'</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>a6d2f6834f22e574</t>
+          <t>4a818d7951649b77</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2692,22 +2692,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S44D</t>
+          <t>P39D</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>VERT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>mutant non eligible : mecanisme_pH='INDETERMINE' attendu 'robuste' ; verdict_carboxylate='INDETERMINE' attendu 'VERT'</t>
+          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste'</t>
         </is>
       </c>
     </row>
@@ -2719,12 +2719,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>f6d5f550a210fd48</t>
+          <t>cd272a8fd929c7ee</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2734,22 +2734,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>S38D</t>
+          <t>N21E</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>ROUGE</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>mutant non eligible : mecanisme_pH='INDETERMINE' attendu 'robuste' ; verdict_carboxylate='INDETERMINE' attendu 'VERT'</t>
+          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste' ; verdict_carboxylate='ROUGE' attendu 'VERT'</t>
         </is>
       </c>
     </row>
@@ -2761,12 +2761,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5b295c4d9e1ff73f</t>
+          <t>cd272a8fd929c7ee</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>H23E</t>
+          <t>N21E</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2786,12 +2786,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>ROUGE</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste' ; verdict_carboxylate='INDETERMINE' attendu 'VERT'</t>
+          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste' ; verdict_carboxylate='ROUGE' attendu 'VERT'</t>
         </is>
       </c>
     </row>
@@ -2803,12 +2803,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0</t>
+          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5b295c4d9e1ff73f</t>
+          <t>1e7ab6d8f00c9958</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>H23E</t>
+          <t>S28D</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste' ; verdict_carboxylate='INDETERMINE' attendu 'VERT'</t>
+          <t>mutant non eligible : mecanisme_pH='INDETERMINE' attendu 'robuste' ; verdict_carboxylate='INDETERMINE' attendu 'VERT'</t>
         </is>
       </c>
     </row>
@@ -2845,12 +2845,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>a6334a3a912c86f1</t>
+          <t>a6d2f6834f22e574</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2860,22 +2860,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S15D</t>
+          <t>S44D</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ROUGE</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste' ; verdict_carboxylate='ROUGE' attendu 'VERT'</t>
+          <t>mutant non eligible : mecanisme_pH='INDETERMINE' attendu 'robuste' ; verdict_carboxylate='INDETERMINE' attendu 'VERT'</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>mutant non eligible : mecanisme_pH='INDETERMINE' attendu 'robuste' ; verdict_carboxylate='ROUGE' attendu 'VERT'</t>
+          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste' ; verdict_carboxylate='ROUGE' attendu 'VERT'</t>
         </is>
       </c>
     </row>
@@ -2929,12 +2929,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4a818d7951649b77</t>
+          <t>a6334a3a912c86f1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2944,12 +2944,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>F38D</t>
+          <t>S15D</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste' ; verdict_carboxylate='ROUGE' attendu 'VERT'</t>
+          <t>mutant non eligible : mecanisme_pH='INDETERMINE' attendu 'robuste' ; verdict_carboxylate='ROUGE' attendu 'VERT'</t>
         </is>
       </c>
     </row>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>P39D</t>
+          <t>F38D</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>VERT</t>
+          <t>ROUGE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste'</t>
+          <t>mutant non eligible : mecanisme_pH='absent' attendu 'robuste' ; verdict_carboxylate='ROUGE' attendu 'VERT'</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3084,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3122,7 +3122,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3160,7 +3160,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3198,7 +3198,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3236,7 +3236,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3274,7 +3274,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3312,7 +3312,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3350,7 +3350,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3446,11 +3446,11 @@
     <col width="22" customWidth="1" min="44" max="44"/>
     <col width="26" customWidth="1" min="45" max="45"/>
     <col width="13" customWidth="1" min="46" max="46"/>
-    <col width="13" customWidth="1" min="47" max="47"/>
+    <col width="11" customWidth="1" min="47" max="47"/>
     <col width="23" customWidth="1" min="48" max="48"/>
     <col width="29" customWidth="1" min="49" max="49"/>
     <col width="48" customWidth="1" min="50" max="50"/>
-    <col width="12" customWidth="1" min="51" max="51"/>
+    <col width="10" customWidth="1" min="51" max="51"/>
     <col width="48" customWidth="1" min="52" max="52"/>
   </cols>
   <sheetData>
@@ -3929,7 +3929,7 @@
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.0341</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.0516</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.3882</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.259</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.1664</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.0997</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>fd5dae7987a2388d</t>
+          <t>a6d2f6834f22e574</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5068,24 +5068,32 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>natif</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+          <t>mutant</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>S44D</t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>IEVDPNLPVHEQVFLILEKGTKAEFEALRAGNEKEAEEISKEAVEKIEEAFEKEENPE</t>
+          <t>APTPVEDLSEDEWWELYIKATQWIHEEYKNEKHWEEMYEVMKADHSGRKEEYVAVAQKVLSK</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -5105,52 +5113,48 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>aucune</t>
+          <t>route2 (tentee)</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.993</t>
+          <t>1.191</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-0.01</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>6.26</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>0.23</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0.06</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>1.161</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1.223</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr">
         <is>
-          <t>GLU24</t>
+          <t>ASP44</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>147.1</t>
-        </is>
-      </c>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr">
         <is>
@@ -5159,72 +5163,92 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
+          <t>2/3 rotameres a portee et sans clash</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>3.49</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>4.07</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>sans objet</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
+          <t>VERT</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>sans clash</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>3.08</t>
+        </is>
+      </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>0.502</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.862</t>
+          <t>0.443</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.789</t>
+          <t>0.792</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>S324,S418,I467,S468</t>
+          <t>S324,R353,E388,S418,I467</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>885.6</t>
+          <t>1219.8</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.37</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -5234,27 +5258,27 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>0.842</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.937</t>
+          <t>0.914</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq0_model_0.cif:0.887 | egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq0_model_1.cif:0.887 | egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq0_model_2.cif:0.855</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1__S44D_model_0.cif:0.842 | egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1__S44D_model_1.cif:0.789 | egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1__S44D_model_2.cif:0.803</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.722</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>K322,D323,S324,L325,P349,Q384,Q408,H409,G410,Q411,F412,V417,S418,I438,S440,G441,K465,I467,S468</t>
+          <t>I316,S324,L325,H346,P349,V350,R353,G354,D355,S356,F357,L382,Q384,E388,Q408,H409,Q411,F412,V417,S418,I438,S440,K465,I467</t>
         </is>
       </c>
     </row>
@@ -5271,7 +5295,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq0</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5286,14 +5310,14 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>frere</t>
+          <t>natif</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>IEVDENLPAHEQVFKILEEGTRKEFEARRAGKEEEAERISEEAVKKIEEIFEKEKNPE</t>
+          <t>IEVDPNLPVHEQVFLILEKGTKAEFEALRAGNEKEAEEISKEAVEKIEEAFEKEENPE</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -5303,7 +5327,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -5328,12 +5352,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>0.993</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="R9" t="inlineStr"/>
@@ -5341,12 +5365,12 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -5361,12 +5385,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>159.9</t>
+          <t>147.1</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr"/>
@@ -5392,27 +5416,27 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>0.845</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>0.862</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.789</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -5432,7 +5456,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>916.6</t>
+          <t>885.6</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -5442,7 +5466,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -5452,27 +5476,27 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>0.887</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>0.936</t>
+          <t>0.937</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq1_model_0.cif:0.938 | egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq1_model_1.cif:0.906 | egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq1_model_2.cif:0.922</t>
+          <t>egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq0_model_0.cif:0.887 | egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq0_model_1.cif:0.887 | egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq0_model_2.cif:0.855</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.2955</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>K322,D323,S324,P349,Q384,Q408,H409,G410,Q411,F412,V417,S418,I438,S440,G441,K465,I467,S468</t>
+          <t>K322,D323,S324,L325,P349,Q384,Q408,H409,G410,Q411,F412,V417,S418,I438,S440,G441,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -5489,12 +5513,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9526c9216eb7d6db</t>
+          <t>fd5dae7987a2388d</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5504,24 +5528,24 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>natif</t>
+          <t>frere</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MEILEEEVNGIRVIVDDEGDGYIDVYIFSERDIWSPRVPKDGKSVKEILEEVKEKLK</t>
+          <t>IEVDENLPAHEQVFKILEEGTRKEFEARRAGKEEEAERISEEAVKKIEEIFEKEKNPE</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -5546,12 +5570,12 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>0.956</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="R10" t="inlineStr"/>
@@ -5559,12 +5583,12 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr">
         <is>
-          <t>6.33</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -5574,17 +5598,17 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>ASP32</t>
+          <t>GLU24</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>159.9</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr"/>
@@ -5595,7 +5619,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>CONTACT COURT</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -5610,17 +5634,17 @@
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.002</t>
+          <t>0.704</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>0.738</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -5635,32 +5659,32 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>R353,S418,I467,S468</t>
+          <t>S324,S418,I467,S468</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>722.5</t>
+          <t>916.6</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -5670,27 +5694,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>0.917</t>
+          <t>0.938</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.936</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq0_model_0.cif:0.917 | egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq0_model_1.cif:0.917 | egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq0_model_2.cif:0.896</t>
+          <t>egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq1_model_0.cif:0.938 | egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq1_model_1.cif:0.906 | egfr-dIII-prod02_denovo_l58_fd5dae7987a2388d_seq1_model_2.cif:0.922</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-1.9588</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>P349,R353,L382,Q384,Q408,H409,Q411,F412,A415,V417,S418,I438,S440,G441,K463,K465,I467,S468</t>
+          <t>K322,D323,S324,P349,Q384,Q408,H409,G410,Q411,F412,V417,S418,I438,S440,G441,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5731,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq0</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5722,14 +5746,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>frere</t>
+          <t>natif</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MEILEEEVNGIRVIVDDEGDGNISVYIFSERDIWSPVVPANGKSVKEILEEVKKKLE</t>
+          <t>MEILEEEVNGIRVIVDDEGDGYIDVYIFSERDIWSPRVPKDGKSVKEILEEVKEKLK</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5764,12 +5788,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.867</t>
+          <t>1.022</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="R11" t="inlineStr"/>
@@ -5777,7 +5801,7 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>6.33</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5797,12 +5821,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>99.7</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr"/>
@@ -5828,17 +5852,17 @@
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>1.002</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1.009</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -5858,17 +5882,17 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>673.8</t>
+          <t>722.5</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5888,22 +5912,22 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>0.917</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq1_model_0.cif:0.87 | egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq1_model_1.cif:0.891 | egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq1_model_2.cif:0.87</t>
+          <t>egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq0_model_0.cif:0.917 | egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq0_model_1.cif:0.917 | egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq0_model_2.cif:0.896</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-1.9272</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
@@ -5925,34 +5949,34 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1e7ab6d8f00c9958</t>
+          <t>9526c9216eb7d6db</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01</t>
+          <t>egfr-dIII-prod02</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>natif</t>
+          <t>frere</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MELSAEEMADRIIEVARTGDLEEAAEVSKLSWEEVMKIGEETGRVDEVLAAWLIVGSIVKRGKL</t>
+          <t>MEILEEEVNGIRVIVDDEGDGNISVYIFSERDIWSPVVPANGKSVKEILEEVKKKLE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5972,7 +5996,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>contre-selectif</t>
+          <t>neutre</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5982,12 +6006,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>0.867</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="R12" t="inlineStr"/>
@@ -5995,32 +6019,32 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>6.07</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>GLU34</t>
+          <t>ASP32</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>153.7</t>
+          <t>99.7</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr"/>
@@ -6031,7 +6055,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>hors portee</t>
+          <t>CONTACT COURT</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -6046,59 +6070,59 @@
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.872</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>S418,I467,S468</t>
+          <t>R353,S418,I467,S468</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>875.2</t>
+          <t>673.8</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>0.29</t>
-        </is>
-      </c>
       <c r="AU12" t="inlineStr">
         <is>
           <t>confirmee</t>
@@ -6106,27 +6130,27 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.891</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>0.913</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0_model_0.cif:0.831 | egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0_model_1.cif:0.864 | egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0_model_2.cif:0.864</t>
+          <t>egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq1_model_0.cif:0.87 | egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq1_model_1.cif:0.891 | egfr-dIII-prod02_denovo_l57_9526c9216eb7d6db_seq1_model_2.cif:0.87</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.0341</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>G317,K322,D323,L325,D344,H346,F380,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,G441,K465,I467,S468</t>
+          <t>P349,R353,L382,Q384,Q408,H409,Q411,F412,A415,V417,S418,I438,S440,G441,K463,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -6143,17 +6167,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l59_36dbfc4737a3e59b_seq0</t>
+          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>36dbfc4737a3e59b</t>
+          <t>1e7ab6d8f00c9958</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02</t>
+          <t>egfr-dIII-prod01</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -6165,17 +6189,17 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SSAKEKEKKEEEEVLKLKADLSADVYYKRGWFKNEKEKEEFAEKLYKELKEEEEKKKKS</t>
+          <t>MELSAEEMADRIIEVARTGDLEEAAEVSKLSWEEVMKIGEETGRVDEVLAAWLIVGSIVKRGKL</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -6200,12 +6224,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>0.659</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="R13" t="inlineStr"/>
@@ -6213,7 +6237,7 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -6223,37 +6247,33 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>oui</t>
+          <t>non</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>ASP24</t>
+          <t>GLU34</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>79.1</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>6.4</t>
-        </is>
-      </c>
+          <t>153.7</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr"/>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>ASP24:OD1/ASP20:OD2</t>
+          <t>aucune paire possible</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>hors portee</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -6268,47 +6288,47 @@
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>0.468</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>0.472</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>S324,S418,S468</t>
+          <t>S418,I467,S468</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>921.1</t>
+          <t>875.2</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6318,7 +6338,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -6328,27 +6348,27 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>0.879</t>
+          <t>0.864</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>0.925</t>
+          <t>0.932</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l59_36dbfc4737a3e59b_seq0_model_0.cif:0.879 | egfr-dIII-prod02_denovo_l59_36dbfc4737a3e59b_seq0_model_1.cif:0.879 | egfr-dIII-prod02_denovo_l59_36dbfc4737a3e59b_seq0_model_2.cif:0.845</t>
+          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0_model_0.cif:0.831 | egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0_model_1.cif:0.864 | egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0_model_2.cif:0.864</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.2018</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>I316,G317,I318,F321,K322,S324,L325,P349,L382,Q384,K407,Q408,H409,V417,S418,I438,S440,G441,S468</t>
+          <t>G317,K322,D323,L325,D344,H346,F380,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,G441,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -6365,12 +6385,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l59_36dbfc4737a3e59b_seq0</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5c3ec1903e03c261</t>
+          <t>36dbfc4737a3e59b</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6387,17 +6407,17 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MTKEELWNKIMFEMLWPLPAEERAKRISEIIKEAIEENEKELGKDNEEFKKELEEVLKELEEFLEWTKDSPDWNNPEMKKALEPLKEAIKKM</t>
+          <t>SSAKEKEKKEEEEVLKLKADLSADVYYKRGWFKNEKEKEEFAEKLYKELKEEEEKKKKS</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-9.0</t>
+          <t>-0.01</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -6422,12 +6442,12 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>0.681</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="R14" t="inlineStr"/>
@@ -6435,12 +6455,12 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr">
         <is>
-          <t>3.91</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>6.27</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -6450,23 +6470,27 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>ASP72</t>
+          <t>ASP24</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>109.1</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr"/>
+          <t>79.1</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>6.4</t>
+        </is>
+      </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>aucune paire possible</t>
+          <t>ASP24:OD1/ASP20:OD2</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6486,57 +6510,57 @@
       <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>0.654</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>0.666</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>0.833</t>
+          <t>0.842</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>S418,I467,S468</t>
+          <t>S324,S418,S468</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>833.1</t>
+          <t>921.1</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.26</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6546,27 +6570,27 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>0.696</t>
+          <t>0.879</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>0.925</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq0_model_0.cif:0.589 | egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq0_model_1.cif:0.571 | egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq0_model_2.cif:0.696</t>
+          <t>egfr-dIII-prod02_denovo_l59_36dbfc4737a3e59b_seq0_model_0.cif:0.879 | egfr-dIII-prod02_denovo_l59_36dbfc4737a3e59b_seq0_model_1.cif:0.879 | egfr-dIII-prod02_denovo_l59_36dbfc4737a3e59b_seq0_model_2.cif:0.845</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-1.9859</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>L348,P349,Q384,Q408,H409,Q411,F412,V417,S418,D436,V437,I438,S440,G441,K463,K465,I467,S468</t>
+          <t>I316,G317,I318,F321,K322,S324,L325,P349,L382,Q384,K407,Q408,H409,V417,S418,I438,S440,G441,S468</t>
         </is>
       </c>
     </row>
@@ -6583,12 +6607,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq0</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>a6d2f6834f22e574</t>
+          <t>5c3ec1903e03c261</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6605,17 +6629,17 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>KPTPVEELSEDEWWELYIKATQWIHEEYKNEKNWEEAYEIMKASHSGRKELYVEKAQKALSK</t>
+          <t>MTKEELWNKIMFEMLWPLPAEERAKRISEIIKEAIEENEKELGKDNEEFKKELEEVLKELEEFLEWTKDSPDWNNPEMKKALEPLKEAIKKM</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-9.0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -6640,12 +6664,12 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.678</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="R15" t="inlineStr"/>
@@ -6653,32 +6677,32 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr">
         <is>
-          <t>3.53</t>
+          <t>3.91</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.27</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>non</t>
+          <t>oui</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>GLU50</t>
+          <t>ASP72</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>115.2</t>
+          <t>109.1</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr"/>
@@ -6689,7 +6713,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>hors portee</t>
+          <t>-</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -6704,32 +6728,32 @@
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>0.772</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>0.302</t>
+          <t>0.751</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>S324,R353,S418,I467</t>
+          <t>S418,I467,S468</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
@@ -6739,12 +6763,12 @@
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1139.3</t>
+          <t>833.1</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6754,7 +6778,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6764,27 +6788,27 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>0.696</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>0.949</t>
+          <t>0.866</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0_model_0.cif:0.87 | egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0_model_1.cif:0.87 | egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0_model_2.cif:0.899</t>
+          <t>egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq0_model_0.cif:0.589 | egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq0_model_1.cif:0.571 | egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq0_model_2.cif:0.696</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.0141</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>I316,S324,L325,H346,P349,V350,R353,D355,S356,F357,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,K465,I467</t>
+          <t>L348,P349,Q384,Q408,H409,Q411,F412,V417,S418,D436,V437,I438,S440,G441,K463,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -6801,17 +6825,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>f6d5f550a210fd48</t>
+          <t>a6d2f6834f22e574</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01</t>
+          <t>egfr-dIII-prod02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -6823,17 +6847,17 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MIDVSKLSKEELWWLVIEIIAKYNDPEAQALFSNPETSKYSLEELQKEVEKILKK</t>
+          <t>KPTPVEELSEDEWWELYIKATQWIHEEYKNEKNWEEAYEIMKASHSGRKELYVEKAQKALSK</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -6858,12 +6882,12 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="R16" t="inlineStr"/>
@@ -6871,12 +6895,12 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>6.22</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -6886,17 +6910,17 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>GLU36</t>
+          <t>GLU50</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>115.2</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr"/>
@@ -6922,32 +6946,32 @@
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0.743</t>
+          <t>0.303</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>0.302</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.818</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>S418,I467,S468</t>
+          <t>S324,R353,S418,I467</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
@@ -6957,12 +6981,12 @@
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>710.7</t>
+          <t>1139.3</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -6972,7 +6996,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -6982,27 +7006,27 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>0.899</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>0.949</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0_model_0.cif:0.679 | egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0_model_1.cif:0.642 | egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0_model_2.cif:0.811</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0_model_0.cif:0.87 | egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0_model_1.cif:0.87 | egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0_model_2.cif:0.899</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.6271</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>L348,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,G441,K465,I467,S468</t>
+          <t>I316,S324,L325,H346,P349,V350,R353,D355,S356,F357,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,K465,I467</t>
         </is>
       </c>
     </row>
@@ -7019,39 +7043,39 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1</t>
+          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>a6d2f6834f22e574</t>
+          <t>f6d5f550a210fd48</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02</t>
+          <t>egfr-dIII-prod01</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>frere</t>
+          <t>natif</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>APTPVEDLSEDEWWELYIKATQWIHEEYKNEKHWEEMYEVMKASHSGRKEEYVAVAQKVLSK</t>
+          <t>MIDVSKLSKEELWWLVIEIIAKYNDPEAQALFSNPETSKYSLEELQKEVEKILKK</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -7076,12 +7100,12 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="R17" t="inlineStr"/>
@@ -7089,12 +7113,12 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.22</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
@@ -7104,17 +7128,17 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>GLU50</t>
+          <t>GLU36</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>8.03</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr"/>
@@ -7140,37 +7164,37 @@
       <c r="AI17" t="inlineStr"/>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.743</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.752</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>S324,R353,E388,S418,I467</t>
+          <t>S418,I467,S468</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
@@ -7180,7 +7204,7 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1219.8</t>
+          <t>710.7</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7190,7 +7214,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7200,27 +7224,27 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>0.811</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>0.848</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1_model_0.cif:0.829 | egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1_model_1.cif:0.921 | egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1_model_2.cif:0.829</t>
+          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0_model_0.cif:0.679 | egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0_model_1.cif:0.642 | egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0_model_2.cif:0.811</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.0014</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>I316,S324,L325,H346,P349,V350,R353,G354,D355,S356,F357,L382,Q384,E388,Q408,H409,Q411,F412,V417,S418,I438,S440,K465,I467</t>
+          <t>L348,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,G441,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -7237,39 +7261,47 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1</t>
+          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5b295c4d9e1ff73f</t>
+          <t>f6d5f550a210fd48</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02</t>
+          <t>egfr-dIII-prod01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>frere</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+          <t>mutant</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>S38D</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MLSKEEKDEAEVKIITWFLSVSHEELEAFIKENLDEESQEELRDPSTDMLEYLIELALKNKELLEAILKKYNE</t>
+          <t>MIDVSKLSKEELWWLVIEIIAKYNDPEAQALFSNPETDKYSLEELQKEVEKILKK</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -7279,7 +7311,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -7289,52 +7321,48 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>aucune</t>
+          <t>aucune (hors portee)</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.701</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-1.85</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>4.41</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>6.26</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
+          <t>-2.25</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.699</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.747</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
-          <t>GLU25</t>
+          <t>ASP38</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>8.37</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>147.9</t>
-        </is>
-      </c>
+          <t>3.6</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
       <c r="AB18" t="inlineStr">
         <is>
@@ -7343,42 +7371,62 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>hors portee</t>
-        </is>
-      </c>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
+          <t>0/3 rotameres a portee et sans clash</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>2.87</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>5.12</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>sans objet</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
+          <t>INDETERMINE</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>tous (moins de 2 sans clash)</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.646</t>
+          <t>0.776</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>0.752</t>
+          <t>0.785</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -7393,12 +7441,12 @@
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>561.1</t>
+          <t>710.7</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7408,7 +7456,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7418,27 +7466,27 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>0.736</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1_model_0.cif:0.87 | egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1_model_1.cif:0.891 | egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1_model_2.cif:0.848</t>
+          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0__S38D_model_0.cif:0.736 | egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0__S38D_model_1.cif:0.717 | egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0__S38D_model_2.cif:0.698</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.0555</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>Q384,Q408,H409,Q411,F412,A415,V417,S418,I438,S440,G441,K465,I467,S468</t>
+          <t>L348,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,G441,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -7455,12 +7503,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>5b295c4d9e1ff73f</t>
+          <t>a6d2f6834f22e574</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -7470,24 +7518,24 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>natif</t>
+          <t>frere</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MLSKEEKDEAEVKIITWFLSVSHEELEEFIKKHLPPEVQEKLKDPSTDMLELLIEHALKNPELLEAILKLYES</t>
+          <t>APTPVEDLSEDEWWELYIKATQWIHEEYKNEKHWEEMYEVMKASHSGRKEEYVAVAQKVLSK</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-8.9</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -7512,12 +7560,12 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="R19" t="inlineStr"/>
@@ -7525,12 +7573,12 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>3.38</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
@@ -7540,17 +7588,17 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>GLU25</t>
+          <t>GLU50</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>8.54</t>
+          <t>8.03</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>147.1</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr"/>
@@ -7576,32 +7624,32 @@
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.792</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>S418,I467,S468</t>
+          <t>S324,R353,E388,S418,I467</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
@@ -7611,12 +7659,12 @@
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>558.3</t>
+          <t>1219.8</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -7626,7 +7674,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -7636,27 +7684,27 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.921</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>0.935</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0_model_0.cif:0.783 | egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0_model_1.cif:0.826 | egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0_model_2.cif:0.87</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1_model_0.cif:0.829 | egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1_model_1.cif:0.921 | egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1_model_2.cif:0.829</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.7015</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>Q384,Q408,H409,Q411,F412,A415,V417,S418,I438,S440,G441,K465,I467,S468</t>
+          <t>I316,S324,L325,H346,P349,V350,R353,G354,D355,S356,F357,L382,Q384,E388,Q408,H409,Q411,F412,V417,S418,I438,S440,K465,I467</t>
         </is>
       </c>
     </row>
@@ -7673,12 +7721,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>a6334a3a912c86f1</t>
+          <t>5b295c4d9e1ff73f</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -7688,24 +7736,24 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>natif</t>
+          <t>frere</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>DEEMKEFAIEWVRMSIEWGKKTGEVERALRIARLSAEQFGERSGSEELLEELYEVIKELTE</t>
+          <t>MLSKEEKDEAEVKIITWFLSVSHEELEAFIKENLDEESQEELRDPSTDMLEYLIELALKNKELLEAILKKYNE</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -7730,12 +7778,12 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="R20" t="inlineStr"/>
@@ -7743,12 +7791,12 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>4.41</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
@@ -7758,17 +7806,17 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>GLU17</t>
+          <t>GLU25</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>147.9</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr"/>
@@ -7794,32 +7842,32 @@
       <c r="AI20" t="inlineStr"/>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>0.759</t>
+          <t>0.646</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>0.752</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>R353,S418,K443,I467,S468</t>
+          <t>S418,I467,S468</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
@@ -7829,12 +7877,12 @@
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1082.2</t>
+          <t>561.1</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -7844,7 +7892,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -7854,27 +7902,27 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>0.891</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0_model_0.cif:0.909 | egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0_model_1.cif:0.894 | egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0_model_2.cif:0.864</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1_model_0.cif:0.87 | egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1_model_1.cif:0.891 | egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1_model_2.cif:0.848</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.417</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>L325,H346,P349,V350,R353,D355,L382,Q384,H409,G410,Q411,A415,V417,S418,L419,N420,I438,S440,G441,K443,K465,I467,S468</t>
+          <t>Q384,Q408,H409,Q411,F412,A415,V417,S418,I438,S440,G441,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -7891,12 +7939,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5c3ec1903e03c261</t>
+          <t>5b295c4d9e1ff73f</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -7906,24 +7954,32 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>frere</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+          <t>mutant</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>H23E</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MTGEELWNQLMFTMLWPLPPEEIAQKISEIIEKAIKEAKEKYGEDNEEFKKELEKVLEELKEFLEWTKDSPDWSHPAMEEAIKPLEKAIKEM</t>
+          <t>MLSKEEKDEAEVKIITWFLSVSEEELEAFIKENLDEESQEELRDPSTDMLEYLIELALKNKELLEAILKKYNE</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-11.0</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -7943,52 +7999,48 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>aucune</t>
+          <t>aucune (hors portee)</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.687</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-0.86</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>5.42</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>6.28</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>oui</t>
-        </is>
-      </c>
+          <t>-1.71</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0.687</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>0.688</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
-          <t>ASP72</t>
+          <t>GLU23</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>120.7</t>
-        </is>
-      </c>
+          <t>5.24</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr"/>
       <c r="AA21" t="inlineStr"/>
       <c r="AB21" t="inlineStr">
         <is>
@@ -7997,62 +8049,82 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
+          <t>0/3 rotameres a portee et sans clash</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>5.18</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>sans objet</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
+          <t>INDETERMINE</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>sans clash</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>0.717</t>
+          <t>0.755</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>S418,K443,I467,S468</t>
+          <t>S418,I467,S468</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>903.8</t>
+          <t>561.1</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -8062,7 +8134,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -8072,27 +8144,27 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>0.929</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.925</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq1_model_0.cif:0.875 | egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq1_model_1.cif:0.893 | egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq1_model_2.cif:0.929</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1__H23E_model_0.cif:0.87 | egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1__H23E_model_1.cif:0.87 | egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1__H23E_model_2.cif:0.848</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.3619</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>L348,Q384,Q408,H409,Q411,F412,V417,S418,D436,V437,I438,S440,G441,K443,K463,K465,I467,S468</t>
+          <t>Q384,Q408,H409,Q411,F412,A415,V417,S418,I438,S440,G441,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -8109,12 +8181,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>a6334a3a912c86f1</t>
+          <t>5b295c4d9e1ff73f</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -8124,24 +8196,24 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>frere</t>
+          <t>natif</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>DKEMEEFAEEWVRMSLEWGKKTGDVERAVRIARLSAEQFGERSGSKELLERLEKIIKELTE</t>
+          <t>MLSKEEKDEAEVKIITWFLSVSHEELEEFIKKHLPPEVQEKLKDPSTDMLELLIEHALKNPELLEAILKLYES</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-8.9</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -8166,12 +8238,12 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>0.687</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="R22" t="inlineStr"/>
@@ -8179,12 +8251,12 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>6.19</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
@@ -8194,17 +8266,17 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>GLU17</t>
+          <t>GLU25</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>8.54</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>113.8</t>
+          <t>147.1</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr"/>
@@ -8230,47 +8302,47 @@
       <c r="AI22" t="inlineStr"/>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>0.771</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>S324,R353,S418,K443,I467,S468</t>
+          <t>S418,I467,S468</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1107.2</t>
+          <t>558.3</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -8280,7 +8352,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -8290,27 +8362,27 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>0.957</t>
+          <t>0.932</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1_model_0.cif:0.806 | egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1_model_1.cif:0.821 | egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1_model_2.cif:0.851</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0_model_0.cif:0.783 | egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0_model_1.cif:0.826 | egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0_model_2.cif:0.87</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.1487</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>I316,S324,L325,H346,P349,V350,R353,D355,L382,Q384,H409,G410,Q411,F412,A415,V417,S418,L419,N420,I438,S440,G441,K443,K465,I467,S468</t>
+          <t>Q384,Q408,H409,Q411,F412,A415,V417,S418,I438,S440,G441,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -8327,12 +8399,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4a818d7951649b77</t>
+          <t>5b295c4d9e1ff73f</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -8342,24 +8414,32 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>frere</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+          <t>mutant</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>H23E</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MSEIEKKVLEAIETYEKFLGGYNLSAEEKGMQAIIFWFPKDGKTISDEEFDEMVKVAIELGKKE</t>
+          <t>MLSKEEKDEAEVKIITWFLSVSEEELEEFIKKHLPPEVQEKLKDPSTDMLELLIEHALKNPELLEAILKLYES</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>73</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-8.9</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -8379,52 +8459,48 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>aucune</t>
+          <t>aucune (hors portee)</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.691</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-1.85</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>4.39</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>6.24</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>non</t>
-        </is>
-      </c>
+          <t>-1.51</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>0.14</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0.69</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>0.694</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
       <c r="X23" t="inlineStr">
         <is>
-          <t>GLU49</t>
+          <t>GLU23</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>10.11</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>98.1</t>
-        </is>
-      </c>
+          <t>5.26</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr"/>
       <c r="AB23" t="inlineStr">
         <is>
@@ -8433,62 +8509,82 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>hors portee</t>
-        </is>
-      </c>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
+          <t>0/3 rotameres a portee et sans clash</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>5.09</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>0.42</t>
+        </is>
+      </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>sans objet</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
+          <t>INDETERMINE</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>sans clash</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>0.22</t>
+        </is>
+      </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.769</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.786</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>R353,S418,K443,I467,S468</t>
+          <t>S418,I467,S468</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>924.9</t>
+          <t>558.3</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -8498,7 +8594,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -8508,27 +8604,27 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>0.913</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>0.923</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1_model_0.cif:0.831 | egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1_model_1.cif:0.815 | egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1_model_2.cif:0.892</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0__H23E_model_0.cif:0.913 | egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0__H23E_model_1.cif:0.804 | egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0__H23E_model_2.cif:0.783</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.0979</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>L348,P349,F352,R353,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,G441,K443,K463,K465,I467,S468</t>
+          <t>Q384,Q408,H409,Q411,F412,A415,V417,S418,I438,S440,G441,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -8545,12 +8641,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4a818d7951649b77</t>
+          <t>a6334a3a912c86f1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -8567,17 +8663,17 @@
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MSEIEKKVLKAKEEYEKFLGGYDLSEEEKYMQAIIFWFPKDGKTISDEEFDKMVEIGIKLGKEE</t>
+          <t>DEEMKEFAIEWVRMSIEWGKKTGEVERALRIARLSAEQFGERSGSEELLEELYEVIKELTE</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -8602,12 +8698,12 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>0.709</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="R24" t="inlineStr"/>
@@ -8615,12 +8711,12 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>6.2</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
@@ -8630,17 +8726,17 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>ASP41</t>
+          <t>GLU17</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>9.83</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr"/>
@@ -8666,27 +8762,27 @@
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>0.759</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>0.721</t>
+          <t>0.755</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.783</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -8696,17 +8792,17 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>922.8</t>
+          <t>1082.2</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
@@ -8716,7 +8812,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -8726,27 +8822,27 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>0.909</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>0.948</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0_model_0.cif:0.857 | egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0_model_1.cif:0.889 | egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0_model_2.cif:0.905</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0_model_0.cif:0.909 | egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0_model_1.cif:0.894 | egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0_model_2.cif:0.864</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.5057</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>L325,L348,P349,R353,Q384,Q408,H409,Q411,F412,V417,S418,I438,K443,K463,K465,I467,S468</t>
+          <t>L325,H346,P349,V350,R353,D355,L382,Q384,H409,G410,Q411,A415,V417,S418,L419,N420,I438,S440,G441,K443,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -8758,17 +8854,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>cd272a8fd929c7ee</t>
+          <t>5c3ec1903e03c261</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -8778,32 +8874,24 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>mutant</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>N21E</t>
-        </is>
-      </c>
+          <t>frere</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SEEKKKLTEELIHEIVWDYLEFGSDETLEKYRKRIEEMKKEGKVSEKEYPELEELLEFLSS</t>
+          <t>MTGEELWNQLMFTMLWPLPPEEIAQKISEIIEKAIKEAKEKYGEDNEEFKKELEKVLEELKEFLEWTKDSPDWSHPAMEEAIKPLEKAIKEM</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>92</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-11.0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -8818,53 +8906,57 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>neutre</t>
+          <t>contre-selectif</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>aucune (hors portee)</t>
+          <t>aucune</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>-0.37</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>0.808</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>0.821</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
+          <t>-0.86</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>5.42</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>6.28</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>oui</t>
+        </is>
+      </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>GLU21</t>
+          <t>ASP72</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>7.41</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr"/>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>120.7</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr"/>
       <c r="AB25" t="inlineStr">
         <is>
@@ -8873,82 +8965,62 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0/3 rotameres a portee et sans clash</t>
-        </is>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>5.19</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>5.35</t>
-        </is>
-      </c>
-      <c r="AF25" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>ROUGE</t>
-        </is>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>sans clash</t>
-        </is>
-      </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>0.739</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>0.675</t>
+          <t>0.717</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>0.778</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>S418,I467,S468</t>
+          <t>S418,K443,I467,S468</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>722.6</t>
+          <t>903.8</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -8963,28 +9035,32 @@
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>non mesuree</t>
+          <t>confirmee</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
+          <t>0.929</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr"/>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq1_model_0.cif:0.875 | egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq1_model_1.cif:0.893 | egfr-dIII-prod02_denovo_l92_5c3ec1903e03c261_seq1_model_2.cif:0.929</t>
+        </is>
+      </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.104</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>P349,Q384,Q408,H409,Q411,F412,V417,S418,D436,V437,I438,S440,K463,K465,I467,S468</t>
+          <t>L348,Q384,Q408,H409,Q411,F412,V417,S418,D436,V437,I438,S440,G441,K443,K463,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -8996,17 +9072,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>cd272a8fd929c7ee</t>
+          <t>a6334a3a912c86f1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -9016,22 +9092,14 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>mutant</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>N21E</t>
-        </is>
-      </c>
+          <t>frere</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SSEKKKKFDELIHDIVWRYLEFGSQETLEEARKKVEEAKKNGEISEEQYPEAVELLDFLSS</t>
+          <t>DKEMEEFAEEWVRMSLEWGKKTGDVERAVRIARLSAEQFGERSGSKELLERLEKIIKELTE</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -9041,7 +9109,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -9056,53 +9124,57 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>neutre</t>
+          <t>contre-selectif</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>aucune (hors portee)</t>
+          <t>aucune</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>0.713</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>-0.36</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>0.821</t>
-        </is>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>0.824</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
+          <t>-2.75</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>6.19</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>GLU21</t>
+          <t>GLU17</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr"/>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>113.8</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr"/>
       <c r="AB26" t="inlineStr">
         <is>
@@ -9111,47 +9183,27 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>0/3 rotameres a portee et sans clash</t>
-        </is>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>5.16</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>5.81</t>
-        </is>
-      </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
-      </c>
+          <t>hors portee</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>ROUGE</t>
-        </is>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>sans clash</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>0.622</t>
+          <t>0.753</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>0.745</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
@@ -9161,32 +9213,32 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.769</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>S418,I467,S468</t>
+          <t>S324,R353,S418,K443,I467,S468</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>723.5</t>
+          <t>1107.2</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -9196,33 +9248,37 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>non mesuree</t>
+          <t>confirmee</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
+          <t>0.851</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>0.957</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1_model_0.cif:0.806 | egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1_model_1.cif:0.821 | egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1_model_2.cif:0.851</t>
+        </is>
+      </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.2152</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>Q384,Q408,H409,Q411,F412,V417,S418,D436,V437,I438,S440,K463,K465,I467,S468</t>
+          <t>I316,S324,L325,H346,P349,V350,R353,D355,L382,Q384,H409,G410,Q411,F412,A415,V417,S418,L419,N420,I438,S440,G441,K443,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -9234,17 +9290,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>a6d2f6834f22e574</t>
+          <t>4a818d7951649b77</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -9254,32 +9310,24 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>mutant</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>S44D</t>
-        </is>
-      </c>
+          <t>frere</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>APTPVEDLSEDEWWELYIKATQWIHEEYKNEKHWEEMYEVMKADHSGRKEEYVAVAQKVLSK</t>
+          <t>MSEIEKKVLEAIETYEKFLGGYNLSAEEKGMQAIIFWFPKDGKTISDEEFDEMVKVAIELGKKE</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -9294,53 +9342,57 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>neutre</t>
+          <t>contre-selectif</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>route2 (tentee)</t>
+          <t>aucune</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.23</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>1.161</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>1.223</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
+          <t>-1.85</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>4.39</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>ASP44</t>
+          <t>GLU49</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr"/>
+          <t>10.11</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>98.1</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr"/>
       <c r="AB27" t="inlineStr">
         <is>
@@ -9349,82 +9401,62 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>2/3 rotameres a portee et sans clash</t>
-        </is>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>3.49</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>4.07</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
+          <t>hors portee</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>VERT</t>
-        </is>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>sans clash</t>
-        </is>
-      </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>3.08</t>
-        </is>
-      </c>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>0.443</t>
+          <t>0.705</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>S324,R353,E388,S418,I467</t>
+          <t>R353,S418,K443,I467,S468</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>1219.8</t>
+          <t>924.9</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
@@ -9434,33 +9466,37 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>non mesuree</t>
+          <t>confirmee</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
+          <t>0.892</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr"/>
+          <t>0.909</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1_model_0.cif:0.831 | egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1_model_1.cif:0.815 | egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1_model_2.cif:0.892</t>
+        </is>
+      </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.3847</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>I316,S324,L325,H346,P349,V350,R353,G354,D355,S356,F357,L382,Q384,E388,Q408,H409,Q411,F412,V417,S418,I438,S440,K465,I467</t>
+          <t>L348,P349,F352,R353,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,G441,K443,K463,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -9472,42 +9508,34 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1e7ab6d8f00c9958</t>
+          <t>4a818d7951649b77</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01</t>
+          <t>egfr-dIII-prod02</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>mutant</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>S28D</t>
-        </is>
-      </c>
+          <t>natif</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MELSAEEMADRIIEVARTGDLEEAAEVDKLSWEEVMKIGEETGRVDEVLAAWLIVGSIVKRGKL</t>
+          <t>MSEIEKKVLKAKEEYEKFLGGYDLSEEEKYMQAIIFWFPKDGKTISDEEFDKMVEIGIKLGKEE</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -9517,7 +9545,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -9527,7 +9555,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -9537,48 +9565,52 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>aucune (hors portee)</t>
+          <t>aucune</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>0.694</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-0.75</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>0.659</t>
-        </is>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>1.023</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
+          <t>-1.89</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>6.24</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>non</t>
+        </is>
+      </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>ASP28</t>
+          <t>ASP41</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr"/>
+          <t>9.83</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>75.2</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr"/>
       <c r="AB28" t="inlineStr">
         <is>
@@ -9587,118 +9619,102 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>0/3 rotameres a portee et sans clash</t>
-        </is>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>3.52</t>
-        </is>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>5.37</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
+          <t>hors portee</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
-        </is>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>IMPOSSIBLE : tous les rotameres clashent</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
+          <t>sans objet</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>0.738</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>0.699</t>
+          <t>0.721</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>S418,I467,S468</t>
+          <t>R353,S418,K443,I467,S468</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>875.2</t>
+          <t>922.8</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>non mesuree</t>
+          <t>confirmee</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
+          <t>0.905</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>0.921</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0_model_0.cif:0.857 | egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0_model_1.cif:0.889 | egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0_model_2.cif:0.905</t>
+        </is>
+      </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.2141</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>G317,K322,D323,L325,D344,H346,F380,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,G441,K465,I467,S468</t>
+          <t>L325,L348,P349,R353,Q384,Q408,H409,Q411,F412,V417,S418,I438,K443,K463,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -9710,17 +9726,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>a6d2f6834f22e574</t>
+          <t>4a818d7951649b77</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -9735,27 +9751,27 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>S44D</t>
+          <t>P39D</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>KPTPVEELSEDEWWELYIKATQWIHEEYKNEKNWEEAYEIMKADHSGRKELYVEKAQKALSK</t>
+          <t>MSEIEKKVLKAKEEYEKFLGGYDLSEEEKYMQAIIFWFDKDGKTISDEEFDKMVEIGIKLGKEE</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -9765,7 +9781,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -9780,27 +9796,27 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="U29" t="inlineStr"/>
@@ -9808,12 +9824,12 @@
       <c r="W29" t="inlineStr"/>
       <c r="X29" t="inlineStr">
         <is>
-          <t>ASP44</t>
+          <t>ASP39</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>6.56</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr"/>
@@ -9830,77 +9846,77 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>VERT</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>IMPOSSIBLE : tous les rotameres clashent</t>
+          <t>sans clash</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>0.742</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>0.801</t>
+          <t>0.725</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>0.706</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>S324,R353,S418,I467</t>
+          <t>R353,S418,K443,I467,S468</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>1139.3</t>
+          <t>922.8</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
@@ -9910,33 +9926,37 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>non mesuree</t>
+          <t>confirmee</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
+          <t>0.905</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr"/>
+          <t>0.856</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0__P39D_model_0.cif:0.905 | egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0__P39D_model_1.cif:0.778 | egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0__P39D_model_2.cif:0.635</t>
+        </is>
+      </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.2051</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>I316,S324,L325,H346,P349,V350,R353,D355,S356,F357,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,K465,I467</t>
+          <t>L325,L348,P349,R353,Q384,Q408,H409,Q411,F412,V417,S418,I438,K443,K463,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -9953,17 +9973,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>f6d5f550a210fd48</t>
+          <t>cd272a8fd929c7ee</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01</t>
+          <t>egfr-dIII-prod02</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -9973,27 +9993,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>S38D</t>
+          <t>N21E</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MIDVSKLSKEELWWLVIEIIAKYNDPEAQALFSNPETDKYSLEELQKEVEKILKK</t>
+          <t>SEEKKKLTEELIHEIVWDYLEFGSDETLEKYRKRIEEMKKEGKVSEKEYPELEELLEFLSS</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -10003,12 +10023,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>contre-selectif</t>
+          <t>neutre</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -10018,27 +10038,27 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>0.816</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>0.699</t>
+          <t>0.808</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>0.821</t>
         </is>
       </c>
       <c r="U30" t="inlineStr"/>
@@ -10046,12 +10066,12 @@
       <c r="W30" t="inlineStr"/>
       <c r="X30" t="inlineStr">
         <is>
-          <t>ASP38</t>
+          <t>GLU21</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr"/>
@@ -10068,57 +10088,57 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>ROUGE</t>
         </is>
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>tous (moins de 2 sans clash)</t>
+          <t>sans clash</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>0.776</t>
+          <t>0.556</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>0.785</t>
+          <t>0.675</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.812</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -10133,12 +10153,12 @@
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>710.7</t>
+          <t>722.6</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
@@ -10148,33 +10168,37 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>non mesuree</t>
+          <t>confirmee</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>0.939</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1__N21E_model_0.cif:0.92 | egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1__N21E_model_1.cif:0.94 | egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1__N21E_model_2.cif:0.92</t>
+        </is>
+      </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.1509</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>L348,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,G441,K465,I467,S468</t>
+          <t>P349,Q384,Q408,H409,Q411,F412,V417,S418,D436,V437,I438,S440,K463,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -10191,12 +10215,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>5b295c4d9e1ff73f</t>
+          <t>cd272a8fd929c7ee</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -10211,27 +10235,27 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>H23E</t>
+          <t>N21E</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MLSKEEKDEAEVKIITWFLSVSEEELEAFIKENLDEESQEELRDPSTDMLEYLIELALKNKELLEAILKKYNE</t>
+          <t>SSEKKKKFDELIHDIVWRYLEFGSQETLEEARKKVEEAKKNGEISEEQYPEAVELLDFLSS</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -10246,7 +10270,7 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>contre-selectif</t>
+          <t>neutre</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -10256,27 +10280,27 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>0.822</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>0.821</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>0.824</t>
         </is>
       </c>
       <c r="U31" t="inlineStr"/>
@@ -10284,12 +10308,12 @@
       <c r="W31" t="inlineStr"/>
       <c r="X31" t="inlineStr">
         <is>
-          <t>GLU23</t>
+          <t>GLU21</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr"/>
@@ -10306,22 +10330,22 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>ROUGE</t>
         </is>
       </c>
       <c r="AH31" t="inlineStr">
@@ -10331,32 +10355,32 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.622</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>0.755</t>
+          <t>0.774</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -10366,17 +10390,17 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>561.1</t>
+          <t>723.5</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
@@ -10386,33 +10410,37 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>non mesuree</t>
+          <t>confirmee</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr"/>
+          <t>0.938</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0__N21E_model_0.cif:0.86 | egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0__N21E_model_1.cif:0.92 | egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0__N21E_model_2.cif:0.92</t>
+        </is>
+      </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.1064</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>Q384,Q408,H409,Q411,F412,A415,V417,S418,I438,S440,G441,K465,I467,S468</t>
+          <t>Q384,Q408,H409,Q411,F412,V417,S418,D436,V437,I438,S440,K463,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -10429,17 +10457,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0</t>
+          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5b295c4d9e1ff73f</t>
+          <t>1e7ab6d8f00c9958</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02</t>
+          <t>egfr-dIII-prod01</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -10449,27 +10477,27 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0</t>
+          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>H23E</t>
+          <t>S28D</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MLSKEEKDEAEVKIITWFLSVSEEELEEFIKKHLPPEVQEKLKDPSTDMLELLIEHALKNPELLEAILKLYES</t>
+          <t>MELSAEEMADRIIEVARTGDLEEAAEVDKLSWEEVMKIGEETGRVDEVLAAWLIVGSIVKRGKL</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-8.9</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -10479,7 +10507,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -10494,27 +10522,27 @@
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>0.722</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>0.659</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>1.023</t>
         </is>
       </c>
       <c r="U32" t="inlineStr"/>
@@ -10522,12 +10550,12 @@
       <c r="W32" t="inlineStr"/>
       <c r="X32" t="inlineStr">
         <is>
-          <t>GLU23</t>
+          <t>ASP28</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr"/>
@@ -10544,17 +10572,17 @@
       </c>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
@@ -10564,22 +10592,22 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>sans clash</t>
+          <t>IMPOSSIBLE : tous les rotameres clashent</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>0.709</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>0.699</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
@@ -10589,12 +10617,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>0.857</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -10604,53 +10632,57 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>558.3</t>
+          <t>875.2</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>non mesuree</t>
+          <t>confirmee</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
+          <t>0.881</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>0.93</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0__S28D_model_0.cif:0.881 | egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0__S28D_model_1.cif:0.864 | egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0__S28D_model_2.cif:0.797</t>
+        </is>
+      </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.2409</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>Q384,Q408,H409,Q411,F412,A415,V417,S418,I438,S440,G441,K465,I467,S468</t>
+          <t>G317,K322,D323,L325,D344,H346,F380,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,G441,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -10667,12 +10699,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>a6334a3a912c86f1</t>
+          <t>a6d2f6834f22e574</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -10687,27 +10719,27 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>S15D</t>
+          <t>S44D</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>DEEMKEFAIEWVRMDIEWGKKTGEVERALRIARLSAEQFGERSGSEELLEELYEVIKELTE</t>
+          <t>KPTPVEELSEDEWWELYIKATQWIHEEYKNEKNWEEAYEIMKADHSGRKELYVEKAQKALSK</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -10717,7 +10749,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -10727,32 +10759,32 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>route2 (tentee)</t>
+          <t>aucune (hors portee)</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>1.869</t>
         </is>
       </c>
       <c r="U33" t="inlineStr"/>
@@ -10760,12 +10792,12 @@
       <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
-          <t>ASP15</t>
+          <t>ASP44</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr"/>
@@ -10777,67 +10809,67 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>1/3 rotameres a portee et sans clash</t>
+          <t>0/3 rotameres a portee et sans clash</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>6.14</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>ROUGE</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>sans clash</t>
+          <t>IMPOSSIBLE : tous les rotameres clashent</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>5.523</t>
+          <t>0.804</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>5.493</t>
+          <t>0.801</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>0.783</t>
+          <t>0.818</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>R353,S418,K443,I467,S468</t>
+          <t>S324,R353,S418,I467</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
@@ -10852,7 +10884,7 @@
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>1082.2</t>
+          <t>1139.3</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
@@ -10862,33 +10894,37 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>non mesuree</t>
+          <t>confirmee</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
+          <t>0.913</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr"/>
+          <t>0.937</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0__S44D_model_0.cif:0.913 | egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0__S44D_model_1.cif:0.783 | egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0__S44D_model_2.cif:0.725</t>
+        </is>
+      </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.6411</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>L325,H346,P349,V350,R353,D355,L382,Q384,H409,G410,Q411,A415,V417,S418,L419,N420,I438,S440,G441,K443,K465,I467,S468</t>
+          <t>I316,S324,L325,H346,P349,V350,R353,D355,S356,F357,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,K465,I467</t>
         </is>
       </c>
     </row>
@@ -10905,7 +10941,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -10925,7 +10961,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10935,7 +10971,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>DKEMEEFAEEWVRMDLEWGKKTGDVERAVRIARLSAEQFGERSGSKELLERLEKIIKELTE</t>
+          <t>DEEMKEFAIEWVRMDIEWGKKTGEVERALRIARLSAEQFGERSGSEELLEELYEVIKELTE</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -10945,7 +10981,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -10955,7 +10991,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -10970,27 +11006,27 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.709</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>0.709</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.781</t>
+          <t>0.709</t>
         </is>
       </c>
       <c r="U34" t="inlineStr"/>
@@ -11003,7 +11039,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2.85</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr"/>
@@ -11020,17 +11056,17 @@
       </c>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
@@ -11040,42 +11076,42 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>tous (moins de 2 sans clash)</t>
+          <t>sans clash</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>5.498</t>
+          <t>5.523</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>5.433</t>
+          <t>5.493</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>0.783</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>S324,R353,S418,K443,I467,S468</t>
+          <t>R353,S418,K443,I467,S468</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
@@ -11085,12 +11121,12 @@
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>1107.2</t>
+          <t>1082.2</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
@@ -11100,33 +11136,37 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>non mesuree</t>
+          <t>confirmee</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr"/>
+          <t>0.955</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0__S15D_model_0.cif:0.818 | egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0__S15D_model_1.cif:0.788 | egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0__S15D_model_2.cif:0.833</t>
+        </is>
+      </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.5588</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>I316,S324,L325,H346,P349,V350,R353,D355,L382,Q384,H409,G410,Q411,F412,A415,V417,S418,L419,N420,I438,S440,G441,K443,K465,I467,S468</t>
+          <t>L325,H346,P349,V350,R353,D355,L382,Q384,H409,G410,Q411,A415,V417,S418,L419,N420,I438,S440,G441,K443,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -11143,12 +11183,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4a818d7951649b77</t>
+          <t>a6334a3a912c86f1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -11163,27 +11203,27 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>F38D</t>
+          <t>S15D</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MSEIEKKVLEAIETYEKFLGGYNLSAEEKGMQAIIFWDPKDGKTISDEEFDEMVKVAIELGKKE</t>
+          <t>DKEMEEFAEEWVRMDLEWGKKTGDVERAVRIARLSAEQFGERSGSKELLERLEKIIKELTE</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -11193,7 +11233,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>absent</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -11203,32 +11243,32 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>aucune (hors portee)</t>
+          <t>route2 (tentee)</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.719</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.713</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>1.781</t>
         </is>
       </c>
       <c r="U35" t="inlineStr"/>
@@ -11236,12 +11276,12 @@
       <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
-          <t>ASP38</t>
+          <t>ASP15</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>4.91</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr"/>
@@ -11253,22 +11293,22 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>0/3 rotameres a portee et sans clash</t>
+          <t>1/3 rotameres a portee et sans clash</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>3.16</t>
         </is>
       </c>
       <c r="AG35" t="inlineStr">
@@ -11278,57 +11318,57 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>sans clash</t>
+          <t>tous (moins de 2 sans clash)</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>0.971</t>
+          <t>5.498</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>5.433</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.769</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>R353,S418,K443,I467,S468</t>
+          <t>S324,R353,S418,K443,I467,S468</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>924.9</t>
+          <t>1107.2</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
@@ -11338,33 +11378,37 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>non mesuree</t>
+          <t>confirmee</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
+          <t>0.791</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr"/>
+          <t>0.954</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1__S15D_model_0.cif:0.791 | egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1__S15D_model_1.cif:0.791 | egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1__S15D_model_2.cif:0.791</t>
+        </is>
+      </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.3163</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>L348,P349,F352,R353,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,G441,K443,K463,K465,I467,S468</t>
+          <t>I316,S324,L325,H346,P349,V350,R353,D355,L382,Q384,H409,G410,Q411,F412,A415,V417,S418,L419,N420,I438,S440,G441,K443,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -11381,7 +11425,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -11401,17 +11445,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>P39D</t>
+          <t>F38D</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MSEIEKKVLKAKEEYEKFLGGYDLSEEEKYMQAIIFWFDKDGKTISDEEFDKMVEIGIKLGKEE</t>
+          <t>MSEIEKKVLEAIETYEKFLGGYNLSAEEKGMQAIIFWDPKDGKTISDEEFDEMVKVAIELGKKE</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -11446,12 +11490,12 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -11461,12 +11505,12 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="U36" t="inlineStr"/>
@@ -11474,12 +11518,12 @@
       <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
         <is>
-          <t>ASP39</t>
+          <t>ASP38</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>6.56</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr"/>
@@ -11496,22 +11540,22 @@
       </c>
       <c r="AD36" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AG36" t="inlineStr">
         <is>
-          <t>VERT</t>
+          <t>ROUGE</t>
         </is>
       </c>
       <c r="AH36" t="inlineStr">
@@ -11521,32 +11565,32 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>0.742</t>
+          <t>0.971</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>0.706</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -11556,17 +11600,17 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>922.8</t>
+          <t>924.9</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
@@ -11576,33 +11620,37 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>non mesuree</t>
+          <t>confirmee</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
+          <t>0.846</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>NON MESUREE</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1__F38D_model_0.cif:0.846 | egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1__F38D_model_1.cif:0.8 | egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1__F38D_model_2.cif:0.846</t>
+        </is>
+      </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>non mesure</t>
+          <t>-2.4237</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>L325,L348,P349,R353,Q384,Q408,H409,Q411,F412,V417,S418,I438,K443,K463,K465,I467,S468</t>
+          <t>L348,P349,F352,R353,L382,Q384,Q408,H409,Q411,F412,V417,S418,I438,S440,G441,K443,K463,K465,I467,S468</t>
         </is>
       </c>
     </row>
@@ -11645,7 +11693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S13"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11665,8 +11713,10 @@
     <col width="38" customWidth="1" min="15" max="15"/>
     <col width="15" customWidth="1" min="16" max="16"/>
     <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="17" customWidth="1" min="18" max="18"/>
-    <col width="40" customWidth="1" min="19" max="19"/>
+    <col width="21" customWidth="1" min="18" max="18"/>
+    <col width="21" customWidth="1" min="19" max="19"/>
+    <col width="17" customWidth="1" min="20" max="20"/>
+    <col width="40" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11757,10 +11807,20 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>recuperation_parent</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>recuperation_mutant</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
           <t>cout_structural</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>verdict</t>
         </is>
@@ -11769,67 +11829,67 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>cd272a8fd929c7ee</t>
+          <t>a6d2f6834f22e574</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>N21E</t>
+          <t>S44D</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-2.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>1.191</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>1.714</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>5.19</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5.35</t>
+          <t>4.07</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>ROUGE</t>
+          <t>VERT</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -11839,99 +11899,109 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0/3 rotameres a portee et sans clash</t>
+          <t>2/3 rotameres a portee et sans clash</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-5.9</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.921</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>degrade (carboxylate auto-destructeur)</t>
+          <t>0.842</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>-0.079</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>ameliore</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>cd272a8fd929c7ee</t>
+          <t>f6d5f550a210fd48</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0</t>
+          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>N21E</t>
+          <t>S38D</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-2.89</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.822</t>
+          <t>0.701</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>1.001</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.16</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5.81</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>ROUGE</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>sans clash</t>
+          <t>tous (moins de 2 sans clash)</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -11941,89 +12011,99 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-3.0</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.811</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>degrade (carboxylate auto-destructeur)</t>
+          <t>0.736</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>-0.075</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>neutre (hors portee de H409)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>a6d2f6834f22e574</t>
+          <t>5b295c4d9e1ff73f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>S44D</t>
+          <t>H23E</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-2.85</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-1.71</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.191</t>
+          <t>0.687</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>1.001</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>4.85</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4.07</t>
+          <t>5.18</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>VERT</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -12033,89 +12113,99 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2/3 rotameres a portee et sans clash</t>
+          <t>0/3 rotameres a portee et sans clash</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>-12.0</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.921</t>
+          <t>0.891</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>ameliore</t>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>-0.021</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>neutre (hors portee de H409)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1e7ab6d8f00c9958</t>
+          <t>5b295c4d9e1ff73f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>S28D</t>
+          <t>H23E</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-1.73</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.51</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.659</t>
+          <t>0.687</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.722</t>
+          <t>0.691</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.096</t>
+          <t>1.006</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -12125,7 +12215,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>IMPOSSIBLE : tous les rotameres clashent</t>
+          <t>sans clash</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -12135,69 +12225,79 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-8.9</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-7.0</t>
+          <t>-8.9</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.864</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>degrade (structurellement impossible)</t>
+          <t>0.913</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.043</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>neutre (hors portee de H409)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>a6d2f6834f22e574</t>
+          <t>4a818d7951649b77</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S44D</t>
+          <t>P39D</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-1.54</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.694</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -12207,22 +12307,22 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>VERT</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>IMPOSSIBLE : tous les rotameres clashent</t>
+          <t>sans clash</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -12232,94 +12332,104 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>0.905</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>degrade (structurellement impossible)</t>
+          <t>0.905</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>neutre (hors portee de H409)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>f6d5f550a210fd48</t>
+          <t>cd272a8fd929c7ee</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>S38D</t>
+          <t>N21E</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-2.89</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-2.25</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.808</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>0.816</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>1.01</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>5.19</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>5.35</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>ROUGE</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>tous (moins de 2 sans clash)</t>
+          <t>sans clash</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -12329,89 +12439,99 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-3.0</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>neutre (hors portee de H409)</t>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>degrade (carboxylate auto-destructeur)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>5b295c4d9e1ff73f</t>
+          <t>cd272a8fd929c7ee</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>H23E</t>
+          <t>N21E</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>0.808</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>0.822</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>1.017</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>5.16</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5.18</t>
+          <t>5.81</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>INDETERMINE</t>
+          <t>ROUGE</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -12426,84 +12546,94 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-12.0</t>
+          <t>-5.0</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.891</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>neutre (hors portee de H409)</t>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>degrade (carboxylate auto-destructeur)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5b295c4d9e1ff73f</t>
+          <t>1e7ab6d8f00c9958</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0</t>
+          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>H23E</t>
+          <t>S28D</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-1.73</t>
+          <t>-2.25</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>0.659</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>0.722</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1.006</t>
+          <t>1.096</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>3.52</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -12513,7 +12643,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>sans clash</t>
+          <t>IMPOSSIBLE : tous les rotameres clashent</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -12523,119 +12653,139 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-8.9</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-8.9</t>
+          <t>-7.0</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.864</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>neutre (hors portee de H409)</t>
+          <t>0.881</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>0.017</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>degrade (structurellement impossible)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>a6334a3a912c86f1</t>
+          <t>a6d2f6834f22e574</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>S15D</t>
+          <t>S44D</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>0.686</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>0.692</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.009</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>8.77</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>ROUGE</t>
+          <t>INDETERMINE</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>sans clash</t>
+          <t>IMPOSSIBLE : tous les rotameres clashent</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>1/3 rotameres a portee et sans clash</t>
+          <t>0/3 rotameres a portee et sans clash</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-8.0</t>
+          <t>-3.9</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.909</t>
+          <t>0.899</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>degrade (carboxylate auto-destructeur)</t>
+          <t>0.913</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>0.014</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>degrade (structurellement impossible)</t>
         </is>
       </c>
     </row>
@@ -12647,7 +12797,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -12657,47 +12807,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-2.74</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>0.709</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.719</t>
+          <t>0.709</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>1.008</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>5.54</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>8.77</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -12707,7 +12857,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>tous (moins de 2 sans clash)</t>
+          <t>sans clash</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -12717,20 +12867,30 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>-4.0</t>
+          <t>-8.0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.851</t>
+          <t>0.909</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
+        <is>
+          <t>0.833</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>-0.076</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>degrade (carboxylate auto-destructeur)</t>
         </is>
@@ -12739,62 +12899,62 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4a818d7951649b77</t>
+          <t>a6334a3a912c86f1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>F38D</t>
+          <t>S15D</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>-1.65</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.713</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.719</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.008</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6.17</t>
+          <t>5.54</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -12804,30 +12964,40 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>sans clash</t>
+          <t>tous (moins de 2 sans clash)</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0/3 rotameres a portee et sans clash</t>
+          <t>1/3 rotameres a portee et sans clash</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-6.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0.892</t>
+          <t>0.851</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
+        <is>
+          <t>0.791</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>degrade (carboxylate auto-destructeur)</t>
         </is>
@@ -12841,27 +13011,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>P39D</t>
+          <t>F38D</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-1.89</t>
+          <t>-1.85</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -12871,32 +13041,32 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.009</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3.24</t>
+          <t>6.17</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>VERT</t>
+          <t>ROUGE</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -12921,17 +13091,27 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0.905</t>
+          <t>0.892</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>neutre (hors portee de H409)</t>
+          <t>0.846</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>-0.046</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>degrade (carboxylate auto-destructeur)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:S13"/>
+  <autoFilter ref="A1:U13"/>
   <conditionalFormatting sqref="F2:F13">
     <cfRule type="cellIs" priority="1" operator="greaterThan" dxfId="0">
       <formula>0.5</formula>
@@ -29198,12 +29378,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESM-2</t>
+          <t>ESM-2 — MESURE, hors classement</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NON MESURE, et hors classement par construction. La pseudo-vraisemblance ESM-2 mesure la ressemblance aux proteines naturelles ; nos binders sont de novo et le reglement exige qu'ils ne ressemblent pas au naturel. Classer dessus favoriserait les designs les moins nouveaux. Le temps de calcul est alle au re-scoring orthogonal, qui entre, lui, dans le classement</t>
+          <t>esm2_t33_650M_UR50D, pseudo-vraisemblance par marginales masquees, normalisee par la longueur. PLL/residu de -2,72 a -1,93, mediane -2,21 sur 35 sequences. HORS CLASSEMENT PAR CONSTRUCTION : la metrique mesure la ressemblance aux proteines naturelles, alors que le reglement exige la nouveaute ; classer dessus favoriserait les designs les moins nouveaux. Lue comme detecteur d'anomalie, elle ne remonte RIEN : la plage est etroite (0,8 unite log) et aucune sequence ne sort du lot</t>
         </is>
       </c>
     </row>
@@ -29246,12 +29426,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>NON MESURE — cout structural des mutants</t>
+          <t>Cout structural des mutants — MESURE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>le GPU a ete depense sur les 23 designs natifs, les mutants ayant deja ete disqualifies par PROPKA. Les paires sont incompletes cote structure, par decision assumee</t>
+          <t>les 12 mutants ont ete predits par Boltz-2 apres le report d'echeance de 24 h. Reference : les contacts de la pose AF2 du PARENT, un mutant n'ayant pas de pose AF2. RESULTAT : aucune des 12 mutations ne casse l'interface, cout maximal 0,08 de recuperation de contacts. L'echec des mutants est donc CHIMIQUE, pas structural</t>
         </is>
       </c>
     </row>

--- a/submission/egfr_analysis.xlsx
+++ b/submission/egfr_analysis.xlsx
@@ -3006,7 +3006,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1__S44D</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0</t>
+          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0__S38D</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1__H23E</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0__H23E</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0__P39D</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1__N21E</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0__N21E</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0</t>
+          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0__S28D</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0__S44D</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0__S15D</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1__S15D</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1__F38D</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq1__S44D</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0</t>
+          <t>egfr-dIII-prod01_denovo_l55_f6d5f550a210fd48_seq0__S38D</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq1__H23E</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l73_5b295c4d9e1ff73f_seq0__H23E</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq0__P39D</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -11538,7 +11538,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq1__N21E</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -11800,7 +11800,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l61_cd272a8fd929c7ee_seq0__N21E</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0</t>
+          <t>egfr-dIII-prod01_denovo_l64_1e7ab6d8f00c9958_seq0__S28D</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l62_a6d2f6834f22e574_seq0__S44D</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq0__S15D</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -12848,7 +12848,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l61_a6334a3a912c86f1_seq1__S15D</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1</t>
+          <t>egfr-dIII-prod02_denovo_l64_4a818d7951649b77_seq1__F38D</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
